--- a/public/assets/media/sample-product.xlsx
+++ b/public/assets/media/sample-product.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/raseelalmutairi/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4318857E-44E0-334C-BD1C-3EF20D2EF661}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{213970E3-FF7D-8F4C-A5DD-0A40C98F6D69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15900" xr2:uid="{BF8824F6-71BF-ED4C-9DAB-E712AA5188A2}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="9">
   <si>
     <t>name</t>
   </si>
@@ -44,24 +44,9 @@
     <t>unit_price</t>
   </si>
   <si>
-    <t>purchase_price</t>
-  </si>
-  <si>
-    <t>category</t>
-  </si>
-  <si>
-    <t>brand</t>
-  </si>
-  <si>
     <t>description</t>
   </si>
   <si>
-    <t>Clothings</t>
-  </si>
-  <si>
-    <t>nike</t>
-  </si>
-  <si>
     <t>High quality cotton t-shirt</t>
   </si>
   <si>
@@ -75,6 +60,9 @@
   </si>
   <si>
     <t>KG</t>
+  </si>
+  <si>
+    <t>Sample Product One</t>
   </si>
 </sst>
 </file>
@@ -446,10 +434,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B30B48CF-90A4-E547-821D-22D3533294D4}">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -460,44 +448,43 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H1" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B2">
         <v>120</v>
       </c>
-      <c r="C2">
-        <v>80</v>
+      <c r="C2" t="s">
+        <v>3</v>
       </c>
       <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" t="s">
         <v>7</v>
       </c>
-      <c r="F2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2">
+      <c r="E2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3">
+        <v>120</v>
+      </c>
+      <c r="C3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3">
         <v>50</v>
       </c>
     </row>
